--- a/csv/model/DCC/formula_DCC_MB.xlsx
+++ b/csv/model/DCC/formula_DCC_MB.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="32175" yWindow="990" windowWidth="17280" windowHeight="8880" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="3624" yWindow="2148" windowWidth="17280" windowHeight="8880" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1" calcOnSave="0"/>
 </workbook>
 </file>
 
@@ -440,7 +440,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
+  <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -582,7 +582,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Load factor</t>
+          <t>multiplier_load_factor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -657,7 +657,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Load factor</t>
+          <t>multiplier_load_factor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Load factor</t>
+          <t>multiplier_load_factor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Load factor</t>
+          <t>multiplier_load_factor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Load factor</t>
+          <t>multiplier_load_factor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Load factor</t>
+          <t>multiplier_load_factor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Load factor</t>
+          <t>multiplier_load_factor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Load factor</t>
+          <t>multiplier_load_factor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Load factor</t>
+          <t>multiplier_load_factor</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Load factor</t>
+          <t>multiplier_load_factor</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Load factor</t>
+          <t>multiplier_load_factor</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1709,7 +1709,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2091,7 +2091,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2388,7 +2388,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2473,7 +2473,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2558,7 +2558,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2855,7 +2855,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3619,7 +3619,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3831,7 +3831,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -4298,7 +4298,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -4468,7 +4468,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4595,7 +4595,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4765,7 +4765,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4850,7 +4850,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4892,7 +4892,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4977,7 +4977,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -5062,7 +5062,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -5147,7 +5147,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -5232,7 +5232,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -5359,7 +5359,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -5444,7 +5444,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -5529,7 +5529,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -5656,7 +5656,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -6038,7 +6038,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -6123,7 +6123,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -6208,7 +6208,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -6293,7 +6293,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -6378,7 +6378,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -6420,7 +6420,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -6505,7 +6505,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -6590,7 +6590,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -6675,7 +6675,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -6760,7 +6760,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -6802,7 +6802,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -6972,7 +6972,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -7142,7 +7142,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -7184,7 +7184,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -7269,7 +7269,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -7354,7 +7354,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -7439,7 +7439,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -7524,7 +7524,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -7566,7 +7566,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -7608,7 +7608,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -7650,7 +7650,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -7692,7 +7692,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -7734,7 +7734,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -7818,7 +7818,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -7860,7 +7860,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -7902,7 +7902,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -7944,7 +7944,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -8028,7 +8028,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -8112,7 +8112,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -8154,7 +8154,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -8196,7 +8196,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -8238,7 +8238,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -8280,7 +8280,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -8322,7 +8322,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -8364,7 +8364,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -8406,7 +8406,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -8448,7 +8448,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -8490,7 +8490,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -8532,7 +8532,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -8574,7 +8574,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -8616,7 +8616,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M121" t="n">
@@ -8728,7 +8728,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M122" t="n">
@@ -8798,7 +8798,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M123" t="n">
@@ -8868,7 +8868,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M124" t="n">
@@ -8938,7 +8938,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M125" t="n">
@@ -9008,7 +9008,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M126" t="n">
@@ -9078,7 +9078,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M127" t="n">
@@ -9148,7 +9148,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M128" t="n">
@@ -9218,7 +9218,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M129" t="n">
@@ -9288,7 +9288,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M130" t="n">
@@ -9358,7 +9358,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M131" t="n">
@@ -9428,7 +9428,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M132" t="n">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M133" t="n">
@@ -9568,7 +9568,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M134" t="n">
@@ -9638,7 +9638,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M135" t="n">
@@ -9708,7 +9708,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M136" t="n">
@@ -9778,7 +9778,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M137" t="n">
@@ -9848,7 +9848,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M138" t="n">
@@ -9918,7 +9918,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M139" t="n">
@@ -9988,7 +9988,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M140" t="n">
@@ -10058,7 +10058,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M141" t="n">
@@ -10128,7 +10128,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M142" t="n">
@@ -10198,7 +10198,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M143" t="n">
@@ -10268,7 +10268,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M144" t="n">
@@ -10338,7 +10338,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M145" t="n">
@@ -10408,7 +10408,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M146" t="n">
@@ -10478,7 +10478,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M147" t="n">
@@ -10548,7 +10548,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M148" t="n">
@@ -10618,7 +10618,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M149" t="n">
@@ -10688,7 +10688,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M150" t="n">
@@ -10758,7 +10758,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M151" t="n">
@@ -10828,7 +10828,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M152" t="n">
@@ -10898,7 +10898,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M153" t="n">
@@ -10968,7 +10968,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M154" t="n">
@@ -11038,7 +11038,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M155" t="n">
@@ -11108,7 +11108,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M156" t="n">
@@ -11178,7 +11178,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M157" t="n">
@@ -11248,7 +11248,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M158" t="n">
@@ -11318,7 +11318,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M159" t="n">
@@ -11388,7 +11388,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M160" t="n">
@@ -11458,7 +11458,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M161" t="n">
@@ -11528,7 +11528,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M162" t="n">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M163" t="n">
@@ -11668,7 +11668,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M164" t="n">
@@ -11738,7 +11738,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M165" t="n">
@@ -11808,7 +11808,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M166" t="n">
@@ -11878,7 +11878,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M167" t="n">
@@ -11948,7 +11948,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M168" t="n">
@@ -12018,7 +12018,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M169" t="n">
@@ -12088,7 +12088,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M170" t="n">
@@ -12158,7 +12158,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M171" t="n">
@@ -12228,7 +12228,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M172" t="n">
@@ -12298,7 +12298,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M173" t="n">
@@ -12368,7 +12368,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M174" t="n">
@@ -12438,7 +12438,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M175" t="n">
@@ -12508,7 +12508,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M176" t="n">
@@ -12578,7 +12578,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M177" t="n">
@@ -12648,7 +12648,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M178" t="n">
@@ -12718,7 +12718,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M179" t="n">
@@ -12788,7 +12788,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M180" t="n">
@@ -12858,7 +12858,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M181" t="n">
@@ -12928,7 +12928,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M182" t="n">
@@ -12998,7 +12998,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M183" t="n">
@@ -13068,7 +13068,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M184" t="n">
@@ -13138,7 +13138,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M185" t="n">
@@ -13208,7 +13208,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M186" t="n">
@@ -13278,7 +13278,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M187" t="n">
@@ -13348,7 +13348,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M188" t="n">
@@ -13418,7 +13418,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M189" t="n">
@@ -13488,7 +13488,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M190" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M191" t="n">
@@ -13628,7 +13628,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M192" t="n">
@@ -13698,7 +13698,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M193" t="n">
@@ -13768,7 +13768,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M194" t="n">
@@ -13838,7 +13838,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M195" t="n">
@@ -13908,7 +13908,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M196" t="n">
@@ -13978,7 +13978,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M197" t="n">
@@ -14048,7 +14048,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M198" t="n">
@@ -14118,7 +14118,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M199" t="n">
@@ -14188,7 +14188,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M200" t="n">
@@ -14258,7 +14258,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M201" t="n">
@@ -14328,7 +14328,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M202" t="n">
@@ -14398,7 +14398,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M203" t="n">
@@ -14468,7 +14468,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M204" t="n">
@@ -14538,7 +14538,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M205" t="n">
@@ -14608,7 +14608,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M206" t="n">
@@ -14678,7 +14678,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M207" t="n">
@@ -14748,7 +14748,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M208" t="n">
@@ -14818,7 +14818,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M209" t="n">
@@ -14888,7 +14888,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M210" t="n">
@@ -14958,7 +14958,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M211" t="n">
@@ -15028,7 +15028,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M212" t="n">
@@ -15098,7 +15098,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M213" t="n">
@@ -15168,7 +15168,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M214" t="n">
@@ -15238,7 +15238,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M215" t="n">
@@ -15308,7 +15308,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M216" t="n">
@@ -15378,7 +15378,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M217" t="n">
@@ -15448,7 +15448,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M218" t="n">
@@ -15518,7 +15518,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M219" t="n">
@@ -15588,7 +15588,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M220" t="n">
@@ -15658,7 +15658,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M221" t="n">
@@ -15728,7 +15728,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M222" t="n">
@@ -15798,7 +15798,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M223" t="n">
@@ -15868,7 +15868,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M224" t="n">
@@ -15938,7 +15938,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M225" t="n">
@@ -16008,7 +16008,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M226" t="n">
@@ -16078,7 +16078,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M227" t="n">
@@ -16148,7 +16148,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M228" t="n">
@@ -16218,7 +16218,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -16260,7 +16260,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L230" t="inlineStr">
@@ -16350,7 +16350,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
@@ -16440,7 +16440,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
@@ -16530,7 +16530,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L233" t="inlineStr">
@@ -16620,7 +16620,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -16667,7 +16667,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
@@ -16757,7 +16757,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L236" t="inlineStr">
@@ -16847,7 +16847,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
@@ -16938,7 +16938,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
@@ -17028,7 +17028,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -17070,7 +17070,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L240" t="inlineStr">
@@ -17160,7 +17160,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
@@ -17250,7 +17250,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
@@ -17341,7 +17341,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
@@ -17431,7 +17431,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -17473,7 +17473,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
@@ -17558,7 +17558,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
@@ -17643,7 +17643,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
@@ -17734,7 +17734,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L248" t="inlineStr">
@@ -17819,7 +17819,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -17861,7 +17861,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L250" t="inlineStr">
@@ -17946,7 +17946,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L251" t="inlineStr">
@@ -18031,7 +18031,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">
@@ -18122,7 +18122,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L253" t="inlineStr">
@@ -18207,7 +18207,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -18254,7 +18254,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L255" t="inlineStr">
@@ -18344,7 +18344,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L256" t="inlineStr">
@@ -18434,7 +18434,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L257" t="inlineStr">
@@ -18525,7 +18525,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L258" t="inlineStr">
@@ -18615,7 +18615,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -18657,7 +18657,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L260" t="inlineStr">
@@ -18747,7 +18747,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
@@ -18837,7 +18837,7 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
@@ -18928,7 +18928,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
@@ -19018,7 +19018,7 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -19060,7 +19060,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">
@@ -19150,7 +19150,7 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
@@ -19240,7 +19240,7 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
@@ -19331,7 +19331,7 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
@@ -19421,7 +19421,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -19463,7 +19463,7 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
@@ -19553,7 +19553,7 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
@@ -19643,7 +19643,7 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
@@ -19734,7 +19734,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
@@ -19824,7 +19824,7 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -19866,7 +19866,7 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L275" t="inlineStr">
@@ -19951,7 +19951,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L276" t="inlineStr">
@@ -20041,7 +20041,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L277" t="inlineStr">
@@ -20132,7 +20132,7 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L278" t="inlineStr">
@@ -20222,7 +20222,7 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -20264,7 +20264,7 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L280" t="inlineStr">
@@ -20349,7 +20349,7 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L281" t="inlineStr">
@@ -20439,7 +20439,7 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L282" t="inlineStr">
@@ -20530,7 +20530,7 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L283" t="inlineStr">
@@ -20620,7 +20620,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -20662,7 +20662,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L285" t="inlineStr">
@@ -20747,7 +20747,7 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L286" t="inlineStr">
@@ -20837,7 +20837,7 @@
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L287" t="inlineStr">
@@ -20928,7 +20928,7 @@
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L288" t="inlineStr">
@@ -21018,7 +21018,7 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -21060,7 +21060,7 @@
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L290" t="inlineStr">
@@ -21145,7 +21145,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L291" t="inlineStr">
@@ -21235,7 +21235,7 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L292" t="inlineStr">
@@ -21326,7 +21326,7 @@
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L293" t="inlineStr">
@@ -21416,7 +21416,7 @@
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -21458,7 +21458,7 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L295" t="inlineStr">
@@ -21543,7 +21543,7 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L296" t="inlineStr">
@@ -21633,7 +21633,7 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L297" t="inlineStr">
@@ -21724,7 +21724,7 @@
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L298" t="inlineStr">
@@ -21814,7 +21814,7 @@
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -21856,7 +21856,7 @@
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L300" t="inlineStr">
@@ -21941,7 +21941,7 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L301" t="inlineStr">
@@ -22026,7 +22026,7 @@
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L302" t="inlineStr">
@@ -22117,7 +22117,7 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L303" t="inlineStr">
@@ -22202,7 +22202,7 @@
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -22244,7 +22244,7 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L305" t="inlineStr">
@@ -22329,7 +22329,7 @@
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L306" t="inlineStr">
@@ -22414,7 +22414,7 @@
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L307" t="inlineStr">
@@ -22505,7 +22505,7 @@
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L308" t="inlineStr">
@@ -22590,7 +22590,7 @@
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -22632,7 +22632,7 @@
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L310" t="inlineStr">
@@ -22717,7 +22717,7 @@
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L311" t="inlineStr">
@@ -22802,7 +22802,7 @@
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L312" t="inlineStr">
@@ -22893,7 +22893,7 @@
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L313" t="inlineStr">
@@ -22978,7 +22978,7 @@
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -23020,7 +23020,7 @@
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L315" t="inlineStr">
@@ -23105,7 +23105,7 @@
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L316" t="inlineStr">
@@ -23190,7 +23190,7 @@
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L317" t="inlineStr">
@@ -23281,7 +23281,7 @@
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L318" t="inlineStr">
@@ -23366,7 +23366,7 @@
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L320" t="inlineStr">
@@ -23493,7 +23493,7 @@
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L321" t="inlineStr">
@@ -23578,7 +23578,7 @@
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L322" t="inlineStr">
@@ -23669,7 +23669,7 @@
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L323" t="inlineStr">
@@ -23754,7 +23754,7 @@
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
@@ -23796,7 +23796,7 @@
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L325" t="inlineStr">
@@ -23881,7 +23881,7 @@
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L326" t="inlineStr">
@@ -23966,7 +23966,7 @@
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L327" t="inlineStr">
@@ -24057,7 +24057,7 @@
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L328" t="inlineStr">
@@ -24142,7 +24142,7 @@
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
@@ -24184,7 +24184,7 @@
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L330" t="inlineStr">
@@ -24269,7 +24269,7 @@
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L331" t="inlineStr">
@@ -24354,7 +24354,7 @@
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L332" t="inlineStr">
@@ -24445,7 +24445,7 @@
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L333" t="inlineStr">
@@ -24530,7 +24530,7 @@
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
@@ -24572,7 +24572,7 @@
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L335" t="inlineStr">
@@ -24657,7 +24657,7 @@
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L336" t="inlineStr">
@@ -24742,7 +24742,7 @@
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L337" t="inlineStr">
@@ -24833,7 +24833,7 @@
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L338" t="inlineStr">
@@ -24918,7 +24918,7 @@
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
@@ -24960,7 +24960,7 @@
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L340" t="inlineStr">
@@ -25045,7 +25045,7 @@
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L341" t="inlineStr">
@@ -25130,7 +25130,7 @@
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L342" t="inlineStr">
@@ -25221,7 +25221,7 @@
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L343" t="inlineStr">
@@ -25306,7 +25306,7 @@
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
@@ -25348,7 +25348,7 @@
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L345" t="inlineStr">
@@ -25433,7 +25433,7 @@
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L346" t="inlineStr">
@@ -25518,7 +25518,7 @@
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L347" t="inlineStr">
@@ -25609,7 +25609,7 @@
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L348" t="inlineStr">
@@ -25694,7 +25694,7 @@
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
@@ -25736,7 +25736,7 @@
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L350" t="inlineStr">
@@ -25821,7 +25821,7 @@
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L351" t="inlineStr">
@@ -25906,7 +25906,7 @@
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L352" t="inlineStr">
@@ -25997,7 +25997,7 @@
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L353" t="inlineStr">
@@ -26082,7 +26082,7 @@
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
@@ -26124,7 +26124,7 @@
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L355" t="inlineStr">
@@ -26209,7 +26209,7 @@
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L356" t="inlineStr">
@@ -26294,7 +26294,7 @@
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L357" t="inlineStr">
@@ -26385,7 +26385,7 @@
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L358" t="inlineStr">
@@ -26470,7 +26470,7 @@
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
@@ -26512,7 +26512,7 @@
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L360" t="inlineStr">
@@ -26597,7 +26597,7 @@
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L361" t="inlineStr">
@@ -26682,7 +26682,7 @@
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L362" t="inlineStr">
@@ -26773,7 +26773,7 @@
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L363" t="inlineStr">
@@ -26858,7 +26858,7 @@
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
@@ -26900,7 +26900,7 @@
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L365" t="inlineStr">
@@ -26985,7 +26985,7 @@
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L366" t="inlineStr">
@@ -27070,7 +27070,7 @@
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L367" t="inlineStr">
@@ -27161,7 +27161,7 @@
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L368" t="inlineStr">
@@ -27246,7 +27246,7 @@
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
@@ -27288,7 +27288,7 @@
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L370" t="inlineStr">
@@ -27373,7 +27373,7 @@
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L371" t="inlineStr">
@@ -27458,7 +27458,7 @@
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L372" t="inlineStr">
@@ -27549,7 +27549,7 @@
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L373" t="inlineStr">
@@ -27634,7 +27634,7 @@
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
@@ -27676,7 +27676,7 @@
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L375" t="inlineStr">
@@ -27761,7 +27761,7 @@
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L376" t="inlineStr">
@@ -27846,7 +27846,7 @@
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L377" t="inlineStr">
@@ -27937,7 +27937,7 @@
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L378" t="inlineStr">
@@ -28022,7 +28022,7 @@
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H379" t="inlineStr">
@@ -28064,7 +28064,7 @@
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L380" t="inlineStr">
@@ -28149,7 +28149,7 @@
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L381" t="inlineStr">
@@ -28234,7 +28234,7 @@
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L382" t="inlineStr">
@@ -28325,7 +28325,7 @@
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L383" t="inlineStr">
@@ -28410,7 +28410,7 @@
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
@@ -28452,7 +28452,7 @@
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L385" t="inlineStr">
@@ -28537,7 +28537,7 @@
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L386" t="inlineStr">
@@ -28622,7 +28622,7 @@
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L387" t="inlineStr">
@@ -28707,7 +28707,7 @@
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L388" t="inlineStr">
